--- a/data/historico/semana_326.xlsx
+++ b/data/historico/semana_326.xlsx
@@ -23,14 +23,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$38</definedName>
@@ -1448,16 +1448,16 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>13.75</v>
+        <v>12</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>4</v>
@@ -1466,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>16.36</v>
+        <v>15</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -1490,29 +1490,29 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>31.25</v>
+        <v>31.03</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>4.86</v>
+        <v>4.12</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.43</v>
+        <v>20.6</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="Y7" s="5" t="inlineStr">
         <is>
-          <t>R$ 195,04</t>
+          <t>R$ 225,56</t>
         </is>
       </c>
       <c r="Z7" s="5" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="AB7" s="5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC7" s="5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:24</t>
         </is>
       </c>
     </row>
@@ -1868,25 +1868,25 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>52</v>
+        <v>19.75</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3.25</v>
+        <v>4.08</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>44.23</v>
+        <v>34.18</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
@@ -1916,43 +1916,43 @@
         <v>0</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>32.47</v>
+        <v>24.04</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>5.22</v>
+        <v>3.4</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>5.22</v>
+        <v>13.6</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>2.82</v>
+        <v>1.34</v>
       </c>
       <c r="Y11" s="6" t="inlineStr">
         <is>
-          <t>R$ 78,48</t>
+          <t>R$ 164,75</t>
         </is>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA11" s="6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AB11" s="6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC11" s="6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:53</t>
         </is>
       </c>
     </row>
@@ -5152,13 +5152,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -5348,19 +5348,19 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>31.25</v>
+        <v>31.03</v>
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>25</v>
@@ -5473,10 +5473,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G11" s="29" t="n">
-        <v>32.47</v>
+        <v>24.04</v>
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
@@ -6276,19 +6276,19 @@
         </is>
       </c>
       <c r="C39" s="26" t="n">
-        <v>2847</v>
+        <v>2879</v>
       </c>
       <c r="D39" s="26" t="n">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="26" t="n">
-        <v>4005</v>
+        <v>4039</v>
       </c>
       <c r="G39" s="26" t="n">
-        <v>28.91</v>
+        <v>28.72</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -6427,7 +6427,7 @@
     <row r="45">
       <c r="A45" s="47" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B45" s="47" t="inlineStr">
@@ -6437,84 +6437,84 @@
       </c>
       <c r="C45" s="48" t="inlineStr">
         <is>
-          <t>17751010</t>
+          <t>17767858</t>
         </is>
       </c>
       <c r="D45" s="47" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E45" s="47" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F45" s="47" t="inlineStr">
         <is>
-          <t>Rua RIO PRETO</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G45" s="47" t="inlineStr">
         <is>
-          <t>206 - R</t>
+          <t>258 - R</t>
         </is>
       </c>
       <c r="H45" s="47" t="inlineStr">
         <is>
-          <t>28/09/2026 09:35</t>
+          <t>02/10/2026 15:40</t>
         </is>
       </c>
       <c r="I45" s="47" t="inlineStr">
         <is>
-          <t>28/09/2026 09:40</t>
+          <t>02/10/2026 15:40</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="47" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B46" s="47" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C46" s="48" t="inlineStr">
         <is>
-          <t>17739571</t>
+          <t>17751010</t>
         </is>
       </c>
       <c r="D46" s="47" t="inlineStr">
         <is>
-          <t>423 - SANTA IZABEL</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="E46" s="47" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F46" s="47" t="inlineStr">
         <is>
-          <t>Rua CARMEN SOTO ROJA</t>
+          <t>Rua RIO PRETO</t>
         </is>
       </c>
       <c r="G46" s="47" t="inlineStr">
         <is>
-          <t>326 - R</t>
+          <t>206 - R</t>
         </is>
       </c>
       <c r="H46" s="47" t="inlineStr">
         <is>
-          <t>01/10/2026 08:21</t>
+          <t>28/09/2026 09:35</t>
         </is>
       </c>
       <c r="I46" s="47" t="inlineStr">
         <is>
-          <t>01/10/2026 08:22</t>
+          <t>28/09/2026 09:40</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C47" s="48" t="inlineStr">
         <is>
-          <t>17685255</t>
+          <t>17739571</t>
         </is>
       </c>
       <c r="D47" s="47" t="inlineStr">
@@ -6541,72 +6541,119 @@
       </c>
       <c r="E47" s="47" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F47" s="47" t="inlineStr">
         <is>
-          <t>Rua INTENDENTE JOÃO DA SILVA BRANDÃO</t>
+          <t>Rua CARMEN SOTO ROJA</t>
         </is>
       </c>
       <c r="G47" s="47" t="inlineStr">
         <is>
-          <t>237 - R</t>
+          <t>326 - R</t>
         </is>
       </c>
       <c r="H47" s="47" t="inlineStr">
         <is>
-          <t>28/09/2026 15:50</t>
+          <t>01/10/2026 08:21</t>
         </is>
       </c>
       <c r="I47" s="47" t="inlineStr">
         <is>
-          <t>28/09/2026 15:50</t>
+          <t>01/10/2026 08:22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="47" t="inlineStr">
         <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
+        <is>
+          <t>17685255</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>423 - SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="inlineStr">
+        <is>
+          <t>Q020</t>
+        </is>
+      </c>
+      <c r="F48" s="47" t="inlineStr">
+        <is>
+          <t>Rua INTENDENTE JOÃO DA SILVA BRANDÃO</t>
+        </is>
+      </c>
+      <c r="G48" s="47" t="inlineStr">
+        <is>
+          <t>237 - R</t>
+        </is>
+      </c>
+      <c r="H48" s="47" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:50</t>
+        </is>
+      </c>
+      <c r="I48" s="47" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="47" t="inlineStr">
+        <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B48" s="47" t="inlineStr">
+      <c r="B49" s="47" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C48" s="48" t="inlineStr">
+      <c r="C49" s="48" t="inlineStr">
         <is>
           <t>17711314</t>
         </is>
       </c>
-      <c r="D48" s="47" t="inlineStr">
+      <c r="D49" s="47" t="inlineStr">
         <is>
           <t>407 - MOOCA</t>
         </is>
       </c>
-      <c r="E48" s="47" t="inlineStr">
+      <c r="E49" s="47" t="inlineStr">
         <is>
           <t>Q028</t>
         </is>
       </c>
-      <c r="F48" s="47" t="inlineStr">
+      <c r="F49" s="47" t="inlineStr">
         <is>
           <t>Rua SÃO TOMAZ</t>
         </is>
       </c>
-      <c r="G48" s="47" t="inlineStr">
+      <c r="G49" s="47" t="inlineStr">
         <is>
           <t>775 - R</t>
         </is>
       </c>
-      <c r="H48" s="47" t="inlineStr">
+      <c r="H49" s="47" t="inlineStr">
         <is>
           <t>29/09/2026 14:53</t>
         </is>
       </c>
-      <c r="I48" s="47" t="inlineStr">
+      <c r="I49" s="47" t="inlineStr">
         <is>
           <t>29/09/2026 14:53</t>
         </is>
@@ -6623,6 +6670,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7098,7 +7146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7813,12 +7861,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -7828,10 +7876,10 @@
         <v>22</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -7845,7 +7893,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -7854,7 +7902,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>22</v>
@@ -7863,7 +7911,7 @@
         <v>4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -7877,25 +7925,25 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>22</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -7909,7 +7957,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -7918,16 +7966,16 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>22</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -8101,25 +8149,25 @@
       </c>
       <c r="B32" s="41" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D32" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="41" t="n">
         <v>22</v>
       </c>
       <c r="F32" s="41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32" s="41" t="n">
-        <v>72.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H32" s="41" t="inlineStr">
         <is>
@@ -8133,12 +8181,12 @@
       </c>
       <c r="B33" s="41" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D33" s="41" t="n">
@@ -8151,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>72</v>
+        <v>72.3</v>
       </c>
       <c r="H33" s="41" t="inlineStr">
         <is>
@@ -8165,25 +8213,25 @@
       </c>
       <c r="B34" s="41" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C34" s="41" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D34" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="41" t="n">
         <v>22</v>
       </c>
       <c r="F34" s="41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G34" s="41" t="n">
-        <v>71.2</v>
+        <v>72</v>
       </c>
       <c r="H34" s="41" t="inlineStr">
         <is>
@@ -8197,25 +8245,25 @@
       </c>
       <c r="B35" s="41" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D35" s="41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" s="41" t="n">
         <v>22</v>
       </c>
       <c r="F35" s="41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G35" s="41" t="n">
-        <v>67.2</v>
+        <v>71.2</v>
       </c>
       <c r="H35" s="41" t="inlineStr">
         <is>
@@ -10748,7 +10796,7 @@
         </is>
       </c>
       <c r="D116" s="52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" s="52" t="n">
         <v>0.5</v>
@@ -10760,7 +10808,7 @@
         <v>0.5</v>
       </c>
       <c r="H116" s="52" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="117">
@@ -10844,7 +10892,7 @@
         </is>
       </c>
       <c r="D119" s="52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E119" s="52" t="n">
         <v>0.3</v>
@@ -10856,7 +10904,7 @@
         <v>0.6</v>
       </c>
       <c r="H119" s="52" t="n">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="120">
@@ -10876,7 +10924,7 @@
         </is>
       </c>
       <c r="D120" s="52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E120" s="52" t="n">
         <v>1.5</v>
@@ -10888,7 +10936,7 @@
         <v>3</v>
       </c>
       <c r="H120" s="52" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="121">
@@ -15800,23 +15848,23 @@
       </c>
       <c r="C274" s="52" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D274" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E274" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F274" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E274" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F274" s="52" t="n">
-        <v>2</v>
-      </c>
       <c r="G274" s="52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H274" s="52" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="275">
@@ -15832,23 +15880,23 @@
       </c>
       <c r="C275" s="52" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D275" s="52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E275" s="52" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F275" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G275" s="52" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H275" s="52" t="n">
-        <v>-24</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="276">
@@ -15864,151 +15912,151 @@
       </c>
       <c r="C276" s="52" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D276" s="52" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E276" s="52" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F276" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G276" s="52" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H276" s="52" t="n">
-        <v>-9.199999999999999</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="51" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B277" s="51" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C277" s="51" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D277" s="51" t="n">
+      <c r="A277" s="52" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B277" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C277" s="52" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D277" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="E277" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F277" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G277" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H277" s="51" t="n">
-        <v>3</v>
+      <c r="E277" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F277" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G277" s="52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H277" s="52" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="52" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B278" s="52" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C278" s="52" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D278" s="52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E278" s="52" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F278" s="52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G278" s="52" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H278" s="52" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="52" t="inlineStr">
         <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B279" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C279" s="52" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D279" s="52" t="n">
+        <v>27</v>
+      </c>
+      <c r="E279" s="52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F279" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G279" s="52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H279" s="52" t="n">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="51" t="inlineStr">
+        <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B279" s="52" t="inlineStr">
+      <c r="B280" s="51" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C279" s="52" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D279" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E279" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F279" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G279" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H279" s="52" t="n">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="52" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B280" s="52" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C280" s="52" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D280" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="E280" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F280" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G280" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H280" s="52" t="n">
-        <v>-3</v>
+      <c r="C280" s="51" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D280" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E280" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G280" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" s="51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -16024,23 +16072,23 @@
       </c>
       <c r="C281" s="52" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D281" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E281" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F281" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E281" s="52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F281" s="52" t="n">
-        <v>2</v>
-      </c>
       <c r="G281" s="52" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="H281" s="52" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="282">
@@ -16056,23 +16104,23 @@
       </c>
       <c r="C282" s="52" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D282" s="52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E282" s="52" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F282" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G282" s="52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H282" s="52" t="n">
-        <v>-10</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="283">
@@ -16088,23 +16136,23 @@
       </c>
       <c r="C283" s="52" t="inlineStr">
         <is>
-          <t>Visita no horário de almoço</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D283" s="52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E283" s="52" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F283" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G283" s="52" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H283" s="52" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="284">
@@ -16120,183 +16168,183 @@
       </c>
       <c r="C284" s="52" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D284" s="52" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E284" s="52" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F284" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G284" s="52" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="H284" s="52" t="n">
-        <v>-7.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="51" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B285" s="51" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C285" s="51" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D285" s="51" t="n">
+      <c r="A285" s="52" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B285" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C285" s="52" t="inlineStr">
+        <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D285" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E285" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F285" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G285" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E285" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="F285" s="51" t="n">
+      <c r="H285" s="52" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="52" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B286" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C286" s="52" t="inlineStr">
+        <is>
+          <t>Visita no horário de almoço</t>
+        </is>
+      </c>
+      <c r="D286" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E286" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F286" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G286" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="G285" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H285" s="51" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="51" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B286" s="51" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C286" s="51" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D286" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="E286" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F286" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G286" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H286" s="51" t="n">
-        <v>2</v>
+      <c r="H286" s="52" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="52" t="inlineStr">
         <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B287" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C287" s="52" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D287" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="E287" s="52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F287" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G287" s="52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H287" s="52" t="n">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="51" t="inlineStr">
+        <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B287" s="52" t="inlineStr">
+      <c r="B288" s="51" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C287" s="52" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D287" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="E287" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F287" s="52" t="n">
+      <c r="C288" s="51" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D288" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G287" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H287" s="52" t="n">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="52" t="inlineStr">
+      <c r="E288" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F288" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G288" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H288" s="51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="51" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B288" s="52" t="inlineStr">
+      <c r="B289" s="51" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C288" s="52" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D288" s="52" t="n">
+      <c r="C289" s="51" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D289" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E289" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E288" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F288" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G288" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H288" s="52" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="52" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B289" s="52" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C289" s="52" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D289" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E289" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F289" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G289" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H289" s="52" t="n">
-        <v>-2.4</v>
+      <c r="F289" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" s="51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -16312,23 +16360,23 @@
       </c>
       <c r="C290" s="52" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D290" s="52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E290" s="52" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F290" s="52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G290" s="52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H290" s="52" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="291">
@@ -16344,61 +16392,61 @@
       </c>
       <c r="C291" s="52" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D291" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E291" s="52" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F291" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G291" s="52" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H291" s="52" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="51" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B292" s="51" t="inlineStr">
+      <c r="A292" s="52" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B292" s="52" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C292" s="51" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D292" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E292" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="F292" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G292" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H292" s="51" t="n">
-        <v>5</v>
+      <c r="C292" s="52" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D292" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E292" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F292" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G292" s="52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H292" s="52" t="n">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="52" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B293" s="52" t="inlineStr">
@@ -16408,87 +16456,87 @@
       </c>
       <c r="C293" s="52" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D293" s="52" t="n">
         <v>5</v>
       </c>
       <c r="E293" s="52" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F293" s="52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G293" s="52" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H293" s="52" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="52" t="inlineStr">
         <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B294" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C294" s="52" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D294" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F294" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G294" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H294" s="52" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="51" t="inlineStr">
+        <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B294" s="52" t="inlineStr">
+      <c r="B295" s="51" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C294" s="52" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D294" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E294" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F294" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G294" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H294" s="52" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="52" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B295" s="52" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C295" s="52" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D295" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E295" s="52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F295" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G295" s="52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H295" s="52" t="n">
-        <v>-2.4</v>
+      <c r="C295" s="51" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D295" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F295" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G295" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H295" s="51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="296">
@@ -16504,23 +16552,23 @@
       </c>
       <c r="C296" s="52" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D296" s="52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E296" s="52" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F296" s="52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G296" s="52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H296" s="52" t="n">
-        <v>-1.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="297">
@@ -16536,22 +16584,118 @@
       </c>
       <c r="C297" s="52" t="inlineStr">
         <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D297" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E297" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F297" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G297" s="52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H297" s="52" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="52" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B298" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C298" s="52" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D298" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E298" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F298" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G298" s="52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H298" s="52" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="52" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B299" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C299" s="52" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D299" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E299" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F299" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G299" s="52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H299" s="52" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="52" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B300" s="52" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C300" s="52" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D297" s="52" t="n">
+      <c r="D300" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E297" s="52" t="n">
+      <c r="E300" s="52" t="n">
         <v>1.5</v>
       </c>
-      <c r="F297" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G297" s="52" t="n">
+      <c r="F300" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G300" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="H297" s="52" t="n">
+      <c r="H300" s="52" t="n">
         <v>-3</v>
       </c>
     </row>
@@ -16571,7 +16715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -17131,20 +17275,20 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.69</v>
+        <v>6.06</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Q002, Q006, Q008, Q010, Q011, Q014, Q022, Q030, Q035</t>
+          <t>Q002, Q006, Q008, Q010, Q011, Q014, Q015, Q018, Q021, Q022, Q030, Q035</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -17154,13 +17298,13 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>31.58</v>
+        <v>30.77</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -17547,63 +17691,63 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Bianca Afonso Narbaez</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>419 - CENTRO 5</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Q002, Q003, Q004, Q009, Q013</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Q003, Q004, Q018</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -17613,24 +17757,24 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>422 - VILA TORRES</t>
+          <t>419 - CENTRO 5</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>6.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Q002, Q004, Q005, Q009, Q013, Q014, Q017, Q019, Q020, Q021, Q022, Q023, Q024, Q025, Q026, Q027, Q028, Q030, Q031, Q037</t>
+          <t>Q002, Q003, Q004, Q009, Q013</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -17640,13 +17784,13 @@
         <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>22.22</v>
+        <v>9.59</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -17657,385 +17801,385 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>422 - VILA TORRES</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Q002, Q004, Q005, Q009, Q013, Q014, Q017, Q019, Q020, Q021, Q022, Q023, Q024, Q025, Q026, Q027, Q028, Q030, Q031, Q037</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D22" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E22" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Q001, Q002, Q003, Q004, Q006, Q008, Q010, Q011, Q012, Q013, Q015</t>
         </is>
       </c>
-      <c r="I21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="I22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="n">
         <v>2.56</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="4" t="n">
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>14.29</v>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D23" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E23" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Q014, Q015, Q016, Q025, Q026, Q032, Q033, Q034</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J23" s="5" t="n">
         <v>19.57</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="K23" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="L22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5" t="n">
+      <c r="L23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="n">
         <v>65.93000000000001</v>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>415 - CENTRO 1</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D24" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>3.27</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G24" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Q001, Q002, Q004, Q005, Q006, Q009</t>
         </is>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>46.67</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
+      <c r="L24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
         <v>12.62</v>
       </c>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Q009, Q010, Q012, Q018, Q019</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>414 - PARQUE DOS ERVAIS</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Q009, Q010, Q012, Q018, Q019</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>Tania Maria Montania</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>416 - CENTRO 2</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D26" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E26" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Q003, Q004, Q005</t>
         </is>
       </c>
-      <c r="I25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="n">
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="L25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="4" t="n">
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="n">
         <v>21.88</v>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>410 - SALGADO FILHO</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D27" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>3.75</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F27" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G27" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Q007, Q008, Q009, Q010</t>
         </is>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>24.18</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="L26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="6" t="n">
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="N26" s="6" t="inlineStr">
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>417 - CENTRO 3</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Q003, Q011, Q012</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -18045,24 +18189,24 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.81</v>
+        <v>5.41</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Q001, Q002, Q004, Q005, Q007, Q008, Q009, Q010, Q011, Q013, Q014, Q015, Q016, Q017, Q018, Q019, Q022, Q024</t>
+          <t>Q003, Q011, Q012</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
@@ -18072,13 +18216,13 @@
         <v>0</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -18089,50 +18233,50 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>428 - JARDIM COIMBRA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.35</v>
+        <v>8.81</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Q008, Q028, Q030, Q031, Q032, Q033, Q034, Q038, Q039</t>
+          <t>Q001, Q002, Q004, Q005, Q007, Q008, Q009, Q010, Q011, Q013, Q014, Q015, Q016, Q017, Q018, Q019, Q022, Q024</t>
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -18143,7 +18287,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -18153,40 +18297,40 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>430 - VILA RENÔ</t>
+          <t>428 - JARDIM COIMBRA</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.11</v>
+        <v>5.35</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Q007, Q008, Q009, Q010, Q014, Q015, Q018, Q020, Q021, Q022, Q023, Q024, Q025, Q026</t>
+          <t>Q008, Q028, Q030, Q031, Q032, Q033, Q034, Q038, Q039</t>
         </is>
       </c>
       <c r="I30" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.11</v>
+        <v>2.61</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>29.81</v>
+        <v>37.5</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -18197,7 +18341,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -18207,40 +18351,40 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>427 - JAMIL SALDANHA DERZI</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.22</v>
+        <v>4.11</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Q001, Q004, Q011, Q012, Q016, Q020, Q026, Q036, Q046, Q051, Q055</t>
+          <t>Q007, Q008, Q009, Q010, Q014, Q015, Q018, Q020, Q021, Q022, Q023, Q024, Q025, Q026</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>24.75</v>
+        <v>29.81</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -18251,385 +18395,385 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>427 - JAMIL SALDANHA DERZI</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Q001, Q004, Q011, Q012, Q016, Q020, Q026, Q036, Q046, Q051, Q055</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>432 - ÁREA B - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D33" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E33" s="4" t="n">
         <v>5.06</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F33" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Q012, Q013, Q014, Q015, Q016, Q017, Q018, Q019, Q020, Q021</t>
         </is>
       </c>
-      <c r="I32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4" t="n">
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="L32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="4" t="n">
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4" t="n">
         <v>47.81</v>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D34" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E34" s="5" t="n">
         <v>5.01</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F34" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G34" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Q010, Q011, Q012, Q013, Q014, Q015, Q016, Q017</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J34" s="5" t="n">
         <v>15.15</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="K34" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5" t="n">
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>423 - SANTA IZABEL</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Q009, Q011, Q016, Q017, Q018, Q019, Q020, Q021, Q022, Q023, Q024, Q027, Q028</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>423 - SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Q009, Q011, Q016, Q017, Q018, Q019, Q020, Q021, Q022, Q023, Q024, Q027, Q028</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>424 - SÃO JOÃO</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D36" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>6.11</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F36" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Q027, Q030, Q031, Q032, Q033, Q034, Q035, Q036</t>
         </is>
       </c>
-      <c r="I35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="4" t="n">
+      <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="L35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="4" t="n">
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="4" t="n">
         <v>52.86</v>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>442 - JARDIM INDEPENDÊNCIA</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D37" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>2.79</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G37" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Q005, Q012, Q015, Q016, Q017, Q018, Q023, Q024, Q025, Q030, Q031, Q038, Q039, Q046, Q047</t>
         </is>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I37" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J37" s="6" t="n">
         <v>48.08</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="K37" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="L36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="6" t="n">
+      <c r="L37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="6" t="n">
         <v>22.39</v>
       </c>
-      <c r="N36" s="6" t="inlineStr">
+      <c r="N37" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>441 - PARQUE DOS IPES</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D38" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E38" s="4" t="n">
         <v>6.72</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Q012, Q015, Q016, Q017, Q019, Q020, Q021, Q031, Q032, Q034, Q037, Q040</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="L37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="4" t="n">
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4" t="n">
         <v>31.53</v>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>445 - JARDIM IVONE</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Q006, Q012, Q013, Q014, Q016, Q018, Q020, Q021, Q022, Q023, Q024, Q027, Q028, Q029, Q030, Q031, Q032, Q033, Q040, Q052</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="L38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="6" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -18639,40 +18783,40 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>439 - BOSQUE CARANDÁ</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>2.41</v>
+        <v>4.46</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Q003, Q004, Q005, Q006, Q007, Q010, Q011, Q013, Q014, Q016, Q017</t>
+          <t>Q006, Q012, Q013, Q014, Q016, Q018, Q020, Q021, Q022, Q023, Q024, Q027, Q028, Q029, Q030, Q031, Q032, Q033, Q040, Q052</t>
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>68.18000000000001</v>
+        <v>35.85</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>19.51</v>
+        <v>28.38</v>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
@@ -18683,115 +18827,115 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>439 - BOSQUE CARANDÁ</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Q003, Q004, Q005, Q006, Q007, Q010, Q011, Q013, Q014, Q016, Q017</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D41" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E41" s="6" t="n">
         <v>3.73</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G41" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>Q019, Q025, Q028, Q029, Q030, Q031, Q032, Q033, Q034, Q037</t>
         </is>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I41" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J41" s="6" t="n">
         <v>44.29</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="K41" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="L40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="6" t="n">
+      <c r="L41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6" t="n">
         <v>9.68</v>
       </c>
-      <c r="N40" s="6" t="inlineStr">
+      <c r="N41" s="6" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>436 - ALEGRETE</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Q002, Q004, Q005, Q006, Q010, Q011, Q012, Q013, Q015</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -18801,40 +18945,40 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>444 - KAMEL SAAD 2</t>
+          <t>436 - ALEGRETE</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>3.98</v>
+        <v>5.68</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Q001, Q002, Q003, Q006, Q007, Q024, Q025, Q026, Q027, Q030, Q034, Q040, Q041, Q042, Q043, Q044</t>
+          <t>Q002, Q004, Q005, Q006, Q010, Q011, Q012, Q013, Q015</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>8.16</v>
+        <v>1.25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>22.83</v>
+        <v>30.43</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
@@ -18845,7 +18989,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -18855,40 +18999,40 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>438 - JARDIM PLANALTO</t>
+          <t>444 - KAMEL SAAD 2</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>6.35</v>
+        <v>3.98</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Q001, Q003, Q004, Q007, Q008, Q011, Q014, Q015, Q016, Q017, Q021, Q027</t>
+          <t>Q001, Q002, Q003, Q006, Q007, Q024, Q025, Q026, Q027, Q030, Q034, Q040, Q041, Q042, Q043, Q044</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>6.06</v>
+        <v>8.16</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>18.85</v>
+        <v>22.83</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
@@ -18899,7 +19043,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -18909,217 +19053,271 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>438 - JARDIM PLANALTO</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>6.27</v>
+        <v>6.35</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
+          <t>Q001, Q003, Q004, Q007, Q008, Q011, Q014, Q015, Q016, Q017, Q021, Q027</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>434 - VILA AUREA</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
           <t>Q002, Q003, Q004, Q005, Q006, Q007, Q008, Q011, Q015, Q019, Q023, Q025</t>
         </is>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="J45" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="K44" s="4" t="n">
+      <c r="K45" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="L44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="4" t="n">
+      <c r="L45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4" t="n">
         <v>32.32</v>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>440 - JARDIM IBIRAPUERA</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D46" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E46" s="5" t="n">
         <v>4.26</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F46" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G46" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Q007, Q009, Q010, Q014, Q015, Q016, Q018, Q019, Q020, Q022, Q023, Q024, Q025, Q027, Q028</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="I46" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="J45" s="5" t="n">
+      <c r="J46" s="5" t="n">
         <v>18.45</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="K46" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="L45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="5" t="n">
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
         <v>35.22</v>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="C50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="C51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C51" s="10" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="C52" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="70" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
+    <row r="58" ht="70" customHeight="1">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N45"/>
+  <autoFilter ref="A2:N46"/>
   <mergeCells count="13">
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A63:C63"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A57:C57"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="B49:C49"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -20635,7 +20833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -20643,7 +20841,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -20653,7 +20851,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS COM DURAÇÃO ACIMA DE 20MIN (12 registros) — AUDITORIA DE POSSÍVEL MANIPULAÇÃO DE HORÁRIO (LANÇAMENTO PELO COMPUTADOR); NO CÁLCULO DE MÉDIA/MEDIANA ENTRAM COMO 20MIN</t>
+          <t>VISITAS COM DURAÇÃO ACIMA DE 20MIN (13 registros) — AUDITORIA DE POSSÍVEL MANIPULAÇÃO DE HORÁRIO (LANÇAMENTO PELO COMPUTADOR); NO CÁLCULO DE MÉDIA/MEDIANA ENTRAM COMO 20MIN</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -20971,47 +21169,47 @@
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>17761374</t>
+          <t>17746454</t>
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q033</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>Rua SANTO ANTONIO SR</t>
+          <t>Rua ADEMIR P JUNIOR</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>30 - R</t>
+          <t>47 - R</t>
         </is>
       </c>
       <c r="H8" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:29</t>
+          <t>01/10/2026 15:15</t>
         </is>
       </c>
       <c r="I8" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:58</t>
+          <t>01/10/2026 15:44</t>
         </is>
       </c>
       <c r="J8" s="29" t="n">
@@ -21021,47 +21219,47 @@
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>17746454</t>
+          <t>17761374</t>
         </is>
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>445 - JARDIM IVONE</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>Rua ADEMIR P JUNIOR</t>
+          <t>Rua SANTO ANTONIO SR</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>47 - R</t>
+          <t>30 - R</t>
         </is>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:15</t>
+          <t>02/10/2026 15:29</t>
         </is>
       </c>
       <c r="I9" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:44</t>
+          <t>02/10/2026 15:58</t>
         </is>
       </c>
       <c r="J9" s="29" t="n">
@@ -21121,47 +21319,47 @@
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>17731458</t>
+          <t>17769628</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Rua JAMIL SALDANHA DERZI</t>
+          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>603 - 1 - TB</t>
+          <t>506 - R</t>
         </is>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:25</t>
+          <t>01/10/2026 15:47</t>
         </is>
       </c>
       <c r="I11" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:49</t>
+          <t>01/10/2026 16:11</t>
         </is>
       </c>
       <c r="J11" s="29" t="n">
@@ -21171,57 +21369,57 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>17744948</t>
+          <t>17731458</t>
         </is>
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>404 - JARDIM DOS ESTADOS</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Rua JOÃO BREMBATI CALVOSO</t>
+          <t>Rua JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>747 - 2 - OU</t>
+          <t>603 - 1 - TB</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 08:58</t>
+          <t>30/09/2026 14:25</t>
         </is>
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 09:21</t>
+          <t>30/09/2026 14:49</t>
         </is>
       </c>
       <c r="J12" s="29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
@@ -21231,95 +21429,145 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>17691418</t>
+          <t>17744948</t>
         </is>
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>404 - JARDIM DOS ESTADOS</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO LUIS</t>
+          <t>Rua JOÃO BREMBATI CALVOSO</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>1081 - 1 - R</t>
+          <t>747 - 2 - OU</t>
         </is>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
-          <t>28/09/2026 08:51</t>
+          <t>01/10/2026 08:58</t>
         </is>
       </c>
       <c r="I13" s="29" t="inlineStr">
         <is>
-          <t>28/09/2026 09:13</t>
+          <t>01/10/2026 09:21</t>
         </is>
       </c>
       <c r="J13" s="29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>17691418</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>Q013</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>Rua SAO LUIS</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="inlineStr">
+        <is>
+          <t>1081 - 1 - R</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="inlineStr">
+        <is>
+          <t>28/09/2026 08:51</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>28/09/2026 09:13</t>
+        </is>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>17710903</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Q032</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>Avenida DA FLORA</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>3174 - R</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>29/09/2026 09:33</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>29/09/2026 09:54</t>
         </is>
       </c>
-      <c r="J14" s="29" t="n">
+      <c r="J15" s="29" t="n">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J14"/>
+  <autoFilter ref="A2:J15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -21336,6 +21584,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25123,7 +25372,7 @@
       </c>
       <c r="H67" s="32" t="inlineStr">
         <is>
-          <t>04 - TB</t>
+          <t>04 - OU</t>
         </is>
       </c>
       <c r="I67" s="32" t="inlineStr">
@@ -26623,7 +26872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -26638,7 +26887,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (95 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (90 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -26792,11 +27041,11 @@
     </row>
     <row r="6">
       <c r="A6" s="40" t="n">
-        <v>116</v>
+        <v>672</v>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
@@ -26816,7 +27065,7 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G6" s="40" t="inlineStr">
@@ -26841,17 +27090,17 @@
       </c>
       <c r="D7" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G7" s="40" t="inlineStr">
@@ -26862,11 +27111,11 @@
     </row>
     <row r="8">
       <c r="A8" s="40" t="n">
-        <v>116</v>
+        <v>3101</v>
       </c>
       <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="C8" s="40" t="inlineStr">
@@ -26876,17 +27125,17 @@
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E8" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G8" s="40" t="inlineStr">
@@ -26897,11 +27146,11 @@
     </row>
     <row r="9">
       <c r="A9" s="40" t="n">
-        <v>672</v>
+        <v>470</v>
       </c>
       <c r="B9" s="40" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C9" s="40" t="inlineStr">
@@ -26932,11 +27181,11 @@
     </row>
     <row r="10">
       <c r="A10" s="40" t="n">
-        <v>3101</v>
+        <v>3037</v>
       </c>
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C10" s="40" t="inlineStr">
@@ -26967,11 +27216,11 @@
     </row>
     <row r="11">
       <c r="A11" s="40" t="n">
-        <v>470</v>
+        <v>1935</v>
       </c>
       <c r="B11" s="40" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C11" s="40" t="inlineStr">
@@ -27002,11 +27251,11 @@
     </row>
     <row r="12">
       <c r="A12" s="40" t="n">
-        <v>3037</v>
+        <v>79</v>
       </c>
       <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C12" s="40" t="inlineStr">
@@ -27037,11 +27286,11 @@
     </row>
     <row r="13">
       <c r="A13" s="40" t="n">
-        <v>1935</v>
+        <v>30</v>
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C13" s="40" t="inlineStr">
@@ -27072,11 +27321,11 @@
     </row>
     <row r="14">
       <c r="A14" s="40" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="B14" s="40" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C14" s="40" t="inlineStr">
@@ -27107,11 +27356,11 @@
     </row>
     <row r="15">
       <c r="A15" s="40" t="n">
-        <v>30</v>
+        <v>1935</v>
       </c>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C15" s="40" t="inlineStr">
@@ -27131,7 +27380,7 @@
       </c>
       <c r="F15" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G15" s="40" t="inlineStr">
@@ -27142,11 +27391,11 @@
     </row>
     <row r="16">
       <c r="A16" s="40" t="n">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="B16" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C16" s="40" t="inlineStr">
@@ -27166,7 +27415,7 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G16" s="40" t="inlineStr">
@@ -27177,11 +27426,11 @@
     </row>
     <row r="17">
       <c r="A17" s="40" t="n">
-        <v>3037</v>
+        <v>116</v>
       </c>
       <c r="B17" s="40" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C17" s="40" t="inlineStr">
@@ -27191,17 +27440,17 @@
       </c>
       <c r="D17" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E17" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G17" s="40" t="inlineStr">
@@ -27212,11 +27461,11 @@
     </row>
     <row r="18">
       <c r="A18" s="40" t="n">
-        <v>1935</v>
+        <v>73</v>
       </c>
       <c r="B18" s="40" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C18" s="40" t="inlineStr">
@@ -27226,12 +27475,12 @@
       </c>
       <c r="D18" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
@@ -27247,11 +27496,11 @@
     </row>
     <row r="19">
       <c r="A19" s="40" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C19" s="40" t="inlineStr">
@@ -27261,12 +27510,12 @@
       </c>
       <c r="D19" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E19" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F19" s="40" t="inlineStr">
@@ -27282,11 +27531,11 @@
     </row>
     <row r="20">
       <c r="A20" s="40" t="n">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C20" s="40" t="inlineStr">
@@ -27296,17 +27545,17 @@
       </c>
       <c r="D20" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G20" s="40" t="inlineStr">
@@ -27331,12 +27580,12 @@
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E21" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
@@ -27352,31 +27601,31 @@
     </row>
     <row r="22">
       <c r="A22" s="40" t="n">
-        <v>73</v>
+        <v>465</v>
       </c>
       <c r="B22" s="40" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D22" s="40" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G22" s="40" t="inlineStr">
@@ -27387,31 +27636,31 @@
     </row>
     <row r="23">
       <c r="A23" s="40" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B23" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D23" s="40" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E23" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F23" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G23" s="40" t="inlineStr">
@@ -27422,26 +27671,26 @@
     </row>
     <row r="24">
       <c r="A24" s="40" t="n">
-        <v>73</v>
+        <v>3035</v>
       </c>
       <c r="B24" s="40" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
@@ -27457,31 +27706,31 @@
     </row>
     <row r="25">
       <c r="A25" s="40" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B25" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D25" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E25" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F25" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G25" s="40" t="inlineStr">
@@ -27492,31 +27741,31 @@
     </row>
     <row r="26">
       <c r="A26" s="40" t="n">
-        <v>116</v>
+        <v>2917</v>
       </c>
       <c r="B26" s="40" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D26" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G26" s="40" t="inlineStr">
@@ -27527,11 +27776,11 @@
     </row>
     <row r="27">
       <c r="A27" s="40" t="n">
-        <v>465</v>
+        <v>99</v>
       </c>
       <c r="B27" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C27" s="40" t="inlineStr">
@@ -27541,12 +27790,12 @@
       </c>
       <c r="D27" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E27" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F27" s="40" t="inlineStr">
@@ -27562,11 +27811,11 @@
     </row>
     <row r="28">
       <c r="A28" s="40" t="n">
-        <v>134</v>
+        <v>3127</v>
       </c>
       <c r="B28" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
@@ -27576,12 +27825,12 @@
       </c>
       <c r="D28" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F28" s="40" t="inlineStr">
@@ -27597,11 +27846,11 @@
     </row>
     <row r="29">
       <c r="A29" s="40" t="n">
-        <v>3035</v>
+        <v>2030</v>
       </c>
       <c r="B29" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C29" s="40" t="inlineStr">
@@ -27611,12 +27860,12 @@
       </c>
       <c r="D29" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E29" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F29" s="40" t="inlineStr">
@@ -27632,11 +27881,11 @@
     </row>
     <row r="30">
       <c r="A30" s="40" t="n">
-        <v>134</v>
+        <v>465</v>
       </c>
       <c r="B30" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr">
@@ -27646,17 +27895,17 @@
       </c>
       <c r="D30" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G30" s="40" t="inlineStr">
@@ -27667,11 +27916,11 @@
     </row>
     <row r="31">
       <c r="A31" s="40" t="n">
-        <v>2917</v>
+        <v>134</v>
       </c>
       <c r="B31" s="40" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C31" s="40" t="inlineStr">
@@ -27702,11 +27951,11 @@
     </row>
     <row r="32">
       <c r="A32" s="40" t="n">
-        <v>99</v>
+        <v>3035</v>
       </c>
       <c r="B32" s="40" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr">
@@ -27737,11 +27986,11 @@
     </row>
     <row r="33">
       <c r="A33" s="40" t="n">
-        <v>3127</v>
+        <v>81</v>
       </c>
       <c r="B33" s="40" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C33" s="40" t="inlineStr">
@@ -27772,11 +28021,11 @@
     </row>
     <row r="34">
       <c r="A34" s="40" t="n">
-        <v>2030</v>
+        <v>142</v>
       </c>
       <c r="B34" s="40" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C34" s="40" t="inlineStr">
@@ -27807,11 +28056,11 @@
     </row>
     <row r="35">
       <c r="A35" s="40" t="n">
-        <v>465</v>
+        <v>2917</v>
       </c>
       <c r="B35" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C35" s="40" t="inlineStr">
@@ -27831,7 +28080,7 @@
       </c>
       <c r="F35" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G35" s="40" t="inlineStr">
@@ -27842,11 +28091,11 @@
     </row>
     <row r="36">
       <c r="A36" s="40" t="n">
-        <v>134</v>
+        <v>465</v>
       </c>
       <c r="B36" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C36" s="40" t="inlineStr">
@@ -27866,7 +28115,7 @@
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G36" s="40" t="inlineStr">
@@ -27877,11 +28126,11 @@
     </row>
     <row r="37">
       <c r="A37" s="40" t="n">
-        <v>3035</v>
+        <v>134</v>
       </c>
       <c r="B37" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C37" s="40" t="inlineStr">
@@ -27901,7 +28150,7 @@
       </c>
       <c r="F37" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G37" s="40" t="inlineStr">
@@ -27912,11 +28161,11 @@
     </row>
     <row r="38">
       <c r="A38" s="40" t="n">
-        <v>81</v>
+        <v>3035</v>
       </c>
       <c r="B38" s="40" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C38" s="40" t="inlineStr">
@@ -27936,7 +28185,7 @@
       </c>
       <c r="F38" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G38" s="40" t="inlineStr">
@@ -27947,11 +28196,11 @@
     </row>
     <row r="39">
       <c r="A39" s="40" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B39" s="40" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C39" s="40" t="inlineStr">
@@ -27961,12 +28210,12 @@
       </c>
       <c r="D39" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="E39" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F39" s="40" t="inlineStr">
@@ -27996,12 +28245,12 @@
       </c>
       <c r="D40" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E40" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F40" s="40" t="inlineStr">
@@ -28017,11 +28266,11 @@
     </row>
     <row r="41">
       <c r="A41" s="40" t="n">
-        <v>465</v>
+        <v>125</v>
       </c>
       <c r="B41" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C41" s="40" t="inlineStr">
@@ -28031,17 +28280,17 @@
       </c>
       <c r="D41" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E41" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F41" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G41" s="40" t="inlineStr">
@@ -28052,11 +28301,11 @@
     </row>
     <row r="42">
       <c r="A42" s="40" t="n">
-        <v>134</v>
+        <v>3127</v>
       </c>
       <c r="B42" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C42" s="40" t="inlineStr">
@@ -28066,17 +28315,17 @@
       </c>
       <c r="D42" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E42" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F42" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G42" s="40" t="inlineStr">
@@ -28087,11 +28336,11 @@
     </row>
     <row r="43">
       <c r="A43" s="40" t="n">
-        <v>3035</v>
+        <v>465</v>
       </c>
       <c r="B43" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C43" s="40" t="inlineStr">
@@ -28101,17 +28350,17 @@
       </c>
       <c r="D43" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E43" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F43" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G43" s="40" t="inlineStr">
@@ -28136,12 +28385,12 @@
       </c>
       <c r="D44" s="40" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E44" s="40" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F44" s="40" t="inlineStr">
@@ -28157,11 +28406,11 @@
     </row>
     <row r="45">
       <c r="A45" s="40" t="n">
-        <v>2917</v>
+        <v>3035</v>
       </c>
       <c r="B45" s="40" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C45" s="40" t="inlineStr">
@@ -28171,17 +28420,17 @@
       </c>
       <c r="D45" s="40" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E45" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F45" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G45" s="40" t="inlineStr">
@@ -28192,11 +28441,11 @@
     </row>
     <row r="46">
       <c r="A46" s="40" t="n">
-        <v>125</v>
+        <v>3035</v>
       </c>
       <c r="B46" s="40" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C46" s="40" t="inlineStr">
@@ -28216,7 +28465,7 @@
       </c>
       <c r="F46" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G46" s="40" t="inlineStr">
@@ -28227,31 +28476,31 @@
     </row>
     <row r="47">
       <c r="A47" s="40" t="n">
-        <v>3127</v>
+        <v>3038</v>
       </c>
       <c r="B47" s="40" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D47" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E47" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F47" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G47" s="40" t="inlineStr">
@@ -28262,26 +28511,26 @@
     </row>
     <row r="48">
       <c r="A48" s="40" t="n">
-        <v>465</v>
+        <v>120</v>
       </c>
       <c r="B48" s="40" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D48" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E48" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F48" s="40" t="inlineStr">
@@ -28297,26 +28546,26 @@
     </row>
     <row r="49">
       <c r="A49" s="40" t="n">
-        <v>134</v>
+        <v>1936</v>
       </c>
       <c r="B49" s="40" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F49" s="40" t="inlineStr">
@@ -28332,26 +28581,26 @@
     </row>
     <row r="50">
       <c r="A50" s="40" t="n">
-        <v>3035</v>
+        <v>2721</v>
       </c>
       <c r="B50" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C50" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F50" s="40" t="inlineStr">
@@ -28367,31 +28616,31 @@
     </row>
     <row r="51">
       <c r="A51" s="40" t="n">
-        <v>3035</v>
+        <v>3038</v>
       </c>
       <c r="B51" s="40" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E51" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F51" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G51" s="40" t="inlineStr">
@@ -28402,11 +28651,11 @@
     </row>
     <row r="52">
       <c r="A52" s="40" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B52" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C52" s="40" t="inlineStr">
@@ -28416,17 +28665,17 @@
       </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E52" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F52" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G52" s="40" t="inlineStr">
@@ -28461,7 +28710,7 @@
       </c>
       <c r="F53" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G53" s="40" t="inlineStr">
@@ -28496,7 +28745,7 @@
       </c>
       <c r="F54" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G54" s="40" t="inlineStr">
@@ -28507,11 +28756,11 @@
     </row>
     <row r="55">
       <c r="A55" s="40" t="n">
-        <v>2721</v>
+        <v>1938</v>
       </c>
       <c r="B55" s="40" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C55" s="40" t="inlineStr">
@@ -28521,12 +28770,12 @@
       </c>
       <c r="D55" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E55" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F55" s="40" t="inlineStr">
@@ -28542,11 +28791,11 @@
     </row>
     <row r="56">
       <c r="A56" s="40" t="n">
-        <v>3038</v>
+        <v>2918</v>
       </c>
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C56" s="40" t="inlineStr">
@@ -28556,12 +28805,12 @@
       </c>
       <c r="D56" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E56" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F56" s="40" t="inlineStr">
@@ -28577,11 +28826,11 @@
     </row>
     <row r="57">
       <c r="A57" s="40" t="n">
-        <v>3128</v>
+        <v>120</v>
       </c>
       <c r="B57" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C57" s="40" t="inlineStr">
@@ -28591,12 +28840,12 @@
       </c>
       <c r="D57" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E57" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F57" s="40" t="inlineStr">
@@ -28612,11 +28861,11 @@
     </row>
     <row r="58">
       <c r="A58" s="40" t="n">
-        <v>120</v>
+        <v>1936</v>
       </c>
       <c r="B58" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C58" s="40" t="inlineStr">
@@ -28626,17 +28875,17 @@
       </c>
       <c r="D58" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F58" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G58" s="40" t="inlineStr">
@@ -28647,11 +28896,11 @@
     </row>
     <row r="59">
       <c r="A59" s="40" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B59" s="40" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C59" s="40" t="inlineStr">
@@ -28661,17 +28910,17 @@
       </c>
       <c r="D59" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E59" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F59" s="40" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G59" s="40" t="inlineStr">
@@ -28682,11 +28931,11 @@
     </row>
     <row r="60">
       <c r="A60" s="40" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B60" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C60" s="40" t="inlineStr">
@@ -28696,12 +28945,12 @@
       </c>
       <c r="D60" s="40" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E60" s="40" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F60" s="40" t="inlineStr">
@@ -28717,11 +28966,11 @@
     </row>
     <row r="61">
       <c r="A61" s="40" t="n">
-        <v>2918</v>
+        <v>3128</v>
       </c>
       <c r="B61" s="40" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C61" s="40" t="inlineStr">
@@ -28752,26 +29001,26 @@
     </row>
     <row r="62">
       <c r="A62" s="40" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="B62" s="40" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C62" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D62" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E62" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F62" s="40" t="inlineStr">
@@ -28787,26 +29036,26 @@
     </row>
     <row r="63">
       <c r="A63" s="40" t="n">
-        <v>1936</v>
+        <v>86</v>
       </c>
       <c r="B63" s="40" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D63" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E63" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F63" s="40" t="inlineStr">
@@ -28822,26 +29071,26 @@
     </row>
     <row r="64">
       <c r="A64" s="40" t="n">
-        <v>1938</v>
+        <v>110</v>
       </c>
       <c r="B64" s="40" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E64" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F64" s="40" t="inlineStr">
@@ -28857,26 +29106,26 @@
     </row>
     <row r="65">
       <c r="A65" s="40" t="n">
-        <v>3038</v>
+        <v>80</v>
       </c>
       <c r="B65" s="40" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D65" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E65" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F65" s="40" t="inlineStr">
@@ -28892,26 +29141,26 @@
     </row>
     <row r="66">
       <c r="A66" s="40" t="n">
-        <v>3128</v>
+        <v>1943</v>
       </c>
       <c r="B66" s="40" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C66" s="40" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D66" s="40" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E66" s="40" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F66" s="40" t="inlineStr">
@@ -28927,11 +29176,11 @@
     </row>
     <row r="67">
       <c r="A67" s="40" t="n">
-        <v>149</v>
+        <v>2789</v>
       </c>
       <c r="B67" s="40" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C67" s="40" t="inlineStr">
@@ -28941,12 +29190,12 @@
       </c>
       <c r="D67" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E67" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F67" s="40" t="inlineStr">
@@ -28962,11 +29211,11 @@
     </row>
     <row r="68">
       <c r="A68" s="40" t="n">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="B68" s="40" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C68" s="40" t="inlineStr">
@@ -28976,12 +29225,12 @@
       </c>
       <c r="D68" s="40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F68" s="40" t="inlineStr">
@@ -28997,11 +29246,11 @@
     </row>
     <row r="69">
       <c r="A69" s="40" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B69" s="40" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C69" s="40" t="inlineStr">
@@ -29032,11 +29281,11 @@
     </row>
     <row r="70">
       <c r="A70" s="40" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B70" s="40" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C70" s="40" t="inlineStr">
@@ -29067,11 +29316,11 @@
     </row>
     <row r="71">
       <c r="A71" s="40" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B71" s="40" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C71" s="40" t="inlineStr">
@@ -29091,7 +29340,7 @@
       </c>
       <c r="F71" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G71" s="40" t="inlineStr">
@@ -29102,11 +29351,11 @@
     </row>
     <row r="72">
       <c r="A72" s="40" t="n">
-        <v>2789</v>
+        <v>149</v>
       </c>
       <c r="B72" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C72" s="40" t="inlineStr">
@@ -29126,7 +29375,7 @@
       </c>
       <c r="F72" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G72" s="40" t="inlineStr">
@@ -29137,11 +29386,11 @@
     </row>
     <row r="73">
       <c r="A73" s="40" t="n">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B73" s="40" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C73" s="40" t="inlineStr">
@@ -29161,7 +29410,7 @@
       </c>
       <c r="F73" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G73" s="40" t="inlineStr">
@@ -29172,11 +29421,11 @@
     </row>
     <row r="74">
       <c r="A74" s="40" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B74" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C74" s="40" t="inlineStr">
@@ -29196,7 +29445,7 @@
       </c>
       <c r="F74" s="40" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G74" s="40" t="inlineStr">
@@ -29207,11 +29456,11 @@
     </row>
     <row r="75">
       <c r="A75" s="40" t="n">
-        <v>86</v>
+        <v>1996</v>
       </c>
       <c r="B75" s="40" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C75" s="40" t="inlineStr">
@@ -29221,12 +29470,12 @@
       </c>
       <c r="D75" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E75" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F75" s="40" t="inlineStr">
@@ -29242,11 +29491,11 @@
     </row>
     <row r="76">
       <c r="A76" s="40" t="n">
-        <v>2789</v>
+        <v>80</v>
       </c>
       <c r="B76" s="40" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C76" s="40" t="inlineStr">
@@ -29256,12 +29505,12 @@
       </c>
       <c r="D76" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E76" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F76" s="40" t="inlineStr">
@@ -29277,11 +29526,11 @@
     </row>
     <row r="77">
       <c r="A77" s="40" t="n">
-        <v>149</v>
+        <v>2789</v>
       </c>
       <c r="B77" s="40" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C77" s="40" t="inlineStr">
@@ -29291,12 +29540,12 @@
       </c>
       <c r="D77" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E77" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F77" s="40" t="inlineStr">
@@ -29312,11 +29561,11 @@
     </row>
     <row r="78">
       <c r="A78" s="40" t="n">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="B78" s="40" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C78" s="40" t="inlineStr">
@@ -29326,12 +29575,12 @@
       </c>
       <c r="D78" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E78" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F78" s="40" t="inlineStr">
@@ -29361,12 +29610,12 @@
       </c>
       <c r="D79" s="40" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E79" s="40" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F79" s="40" t="inlineStr">
@@ -29382,11 +29631,11 @@
     </row>
     <row r="80">
       <c r="A80" s="40" t="n">
-        <v>1996</v>
+        <v>86</v>
       </c>
       <c r="B80" s="40" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C80" s="40" t="inlineStr">
@@ -29406,197 +29655,197 @@
       </c>
       <c r="F80" s="40" t="inlineStr">
         <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G80" s="40" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="41" t="n">
+        <v>110</v>
+      </c>
+      <c r="B81" s="41" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C81" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="41" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F81" s="41" t="inlineStr">
+        <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G80" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="40" t="n">
+      <c r="G81" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="41" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="40" t="inlineStr">
+      <c r="B82" s="41" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="C81" s="40" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D81" s="40" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E81" s="40" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F81" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G81" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="40" t="n">
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="41" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F82" s="41" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G82" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="41" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="41" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F83" s="41" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G83" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="41" t="n">
         <v>2789</v>
       </c>
-      <c r="B82" s="40" t="inlineStr">
+      <c r="B84" s="41" t="inlineStr">
         <is>
           <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
-      <c r="C82" s="40" t="inlineStr">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D82" s="40" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E82" s="40" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F82" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G82" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="40" t="n">
-        <v>124</v>
-      </c>
-      <c r="B83" s="40" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="C83" s="40" t="inlineStr">
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E84" s="41" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F84" s="41" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G84" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="41" t="n">
+        <v>149</v>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D83" s="40" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E83" s="40" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F83" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G83" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="40" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B84" s="40" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C84" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D84" s="40" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E84" s="40" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F84" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G84" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="40" t="n">
-        <v>86</v>
-      </c>
-      <c r="B85" s="40" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D85" s="40" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E85" s="40" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F85" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G85" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="D85" s="41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="41" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F85" s="41" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G85" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="41" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B86" s="41" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C86" s="41" t="inlineStr">
@@ -29627,11 +29876,11 @@
     </row>
     <row r="87">
       <c r="A87" s="41" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="B87" s="41" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C87" s="41" t="inlineStr">
@@ -29662,11 +29911,11 @@
     </row>
     <row r="88">
       <c r="A88" s="41" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B88" s="41" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C88" s="41" t="inlineStr">
@@ -29697,11 +29946,11 @@
     </row>
     <row r="89">
       <c r="A89" s="41" t="n">
-        <v>2789</v>
+        <v>86</v>
       </c>
       <c r="B89" s="41" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C89" s="41" t="inlineStr">
@@ -29732,286 +29981,111 @@
     </row>
     <row r="90">
       <c r="A90" s="41" t="n">
+        <v>157</v>
+      </c>
+      <c r="B90" s="41" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="C90" s="41" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="41" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F90" s="41" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G90" s="41" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="40" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B91" s="40" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D91" s="40" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E91" s="40" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F91" s="40" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G91" s="40" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="40" t="n">
         <v>149</v>
       </c>
-      <c r="B90" s="41" t="inlineStr">
+      <c r="B92" s="40" t="inlineStr">
         <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="C90" s="41" t="inlineStr">
+      <c r="C92" s="40" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D90" s="41" t="inlineStr">
+      <c r="D92" s="40" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="E90" s="41" t="inlineStr">
+      <c r="E92" s="40" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F90" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G90" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="41" t="n">
-        <v>124</v>
-      </c>
-      <c r="B91" s="41" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D91" s="41" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E91" s="41" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F91" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G91" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="41" t="n">
-        <v>161</v>
-      </c>
-      <c r="B92" s="41" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D92" s="41" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E92" s="41" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F92" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G92" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="41" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B93" s="41" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D93" s="41" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E93" s="41" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F93" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G93" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="41" t="n">
-        <v>86</v>
-      </c>
-      <c r="B94" s="41" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E94" s="41" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F94" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G94" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="41" t="n">
-        <v>157</v>
-      </c>
-      <c r="B95" s="41" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D95" s="41" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E95" s="41" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F95" s="41" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G95" s="41" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="40" t="n">
-        <v>1943</v>
-      </c>
-      <c r="B96" s="40" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C96" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D96" s="40" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E96" s="40" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F96" s="40" t="inlineStr">
+      <c r="F92" s="40" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G96" s="40" t="inlineStr">
+      <c r="G92" s="40" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="40" t="n">
-        <v>149</v>
-      </c>
-      <c r="B97" s="40" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D97" s="40" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E97" s="40" t="inlineStr">
-        <is>
-          <t>Quarta</t>
-        </is>
-      </c>
-      <c r="F97" s="40" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G97" s="40" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G97"/>
+  <autoFilter ref="A2:G92"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
